--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:17</t>
+          <t>2026-09-01 03:16:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:17</t>
+          <t>2026-09-01 03:16:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:17</t>
+          <t>2026-09-01 03:16:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:17</t>
+          <t>2026-09-01 03:16:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:17</t>
+          <t>2026-09-01 03:16:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:18</t>
+          <t>2026-09-01 03:16:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:18</t>
+          <t>2026-09-01 03:16:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:18</t>
+          <t>2026-09-01 03:16:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:18</t>
+          <t>2026-09-01 03:16:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:19</t>
+          <t>2026-09-01 03:16:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:21</t>
+          <t>2026-09-01 03:16:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:16</t>
+          <t>2026-09-01 03:32:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:54</t>
+          <t>2026-09-01 15:29:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>971</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:54</t>
+          <t>2026-09-01 15:29:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:54</t>
+          <t>2026-09-01 15:29:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:54</t>
+          <t>2026-09-01 15:29:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:54</t>
+          <t>2026-09-01 15:29:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:55</t>
+          <t>2026-09-01 15:29:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:55</t>
+          <t>2026-09-01 15:29:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:55</t>
+          <t>2026-09-01 15:29:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:55</t>
+          <t>2026-09-01 15:29:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:56</t>
+          <t>2026-09-01 15:29:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:58</t>
+          <t>2026-09-01 15:29:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.81%257</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>279</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:23</t>
+          <t>2026-09-01 15:57:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:23</t>
+          <t>2026-09-01 15:57:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:23</t>
+          <t>2026-09-01 15:57:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:23</t>
+          <t>2026-09-01 15:57:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:23</t>
+          <t>2026-09-01 15:57:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:24</t>
+          <t>2026-09-01 15:57:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:24</t>
+          <t>2026-09-01 15:57:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:24</t>
+          <t>2026-09-01 15:57:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:24</t>
+          <t>2026-09-01 15:57:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:25</t>
+          <t>2026-09-01 15:57:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:27</t>
+          <t>2026-09-01 15:57:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:08</t>
+          <t>2026-09-01 17:54:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:08</t>
+          <t>2026-09-01 17:54:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:08</t>
+          <t>2026-09-01 17:54:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:08</t>
+          <t>2026-09-01 17:54:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:08</t>
+          <t>2026-09-01 17:54:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:09</t>
+          <t>2026-09-01 17:54:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:09</t>
+          <t>2026-09-01 17:54:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:09</t>
+          <t>2026-09-01 17:54:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:09</t>
+          <t>2026-09-01 17:54:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:11</t>
+          <t>2026-09-01 17:54:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:12</t>
+          <t>2026-09-01 17:54:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:19</t>
+          <t>2026-09-01 20:35:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:19</t>
+          <t>2026-09-01 20:35:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:19</t>
+          <t>2026-09-01 20:35:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:19</t>
+          <t>2026-09-01 20:35:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:19</t>
+          <t>2026-09-01 20:35:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:20</t>
+          <t>2026-09-01 20:35:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:20</t>
+          <t>2026-09-01 20:35:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:20</t>
+          <t>2026-09-01 20:35:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:20</t>
+          <t>2026-09-01 20:35:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:21</t>
+          <t>2026-09-01 20:35:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:23</t>
+          <t>2026-09-01 20:35:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
